--- a/JP (Exclude Game)/Dialog/dialog.xlsx
+++ b/JP (Exclude Game)/Dialog/dialog.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="1" state="visible" r:id="rId3"/>
@@ -1181,8 +1181,8 @@
 While poisoned, bleeding, or paralyzed, your opponent won't regenerate. 
 The cubes will not split when they have bad conditions.
 You can use a scroll of reconstruction to an artifact to re-create the artifact.
-You can prevent getting dimmed by increaseing your resistance to sound.
-You can prevent getting insane by increaseing your resistance to mind.
+You can prevent getting dimmed by increasing your resistance to sound.
+You can prevent getting insane by increasing your resistance to mind.
 Blessing a rod is a good idea. But the effects of blessed rods are less dramatic than blessed potions or scrolls.
 When you are wet, fire damages won't be a problem but electric damages will be a serious threat.
 If you vomit too much in a short period, you will suffer anorexia. When you get anoerxia, don't eat. Just drink potions and water.
@@ -1292,7 +1292,9 @@
 少女|はじめての旅|少し怖い。でも楽しい。
 誰か|拾ったあなたへ|あなたがこれを読んでいるなら、世界はまだ続いている。
 不明|お…|おうち…かえう…！
-不明|もう…|もうだめぽ</t>
+不明|もう…|もうだめぽ
+海賊王|財宝| 探せ！ この世の全てをそこに置いてきた！
+海賊|見てろ！| 海賊王に、おれはなる ！！</t>
   </si>
   <si>
     <t xml:space="preserve">Lucia|The Ship That Never Returned|If this bottle reaches someone, I will likely be beneath the sea by then. But the sky was very blue.
@@ -1316,7 +1318,9 @@
 Little Girl|My First Journey|I'm a little scared. But it's fun.
 Someone|To Whoever Finds This|If you are reading this, the world is still going on.
 Unknown|I...|I'm...going...home...!
-Unknown|I'm...|Moudamepo</t>
+Unknown|I'm...|Moudamepo
+Pirate King|My treasure?|Find it! I left everything in this world there!
+Pirate|Watch me|I’m gonna be King of the Pirates!!</t>
   </si>
   <si>
     <t xml:space="preserve">mysilia</t>
@@ -1636,7 +1640,7 @@
 How long has that warmonger's altar been here?
 It seems my old body still remains on the surface.
 Surely you do not believe that gods are omnipotent?
-You are free to believe that the world has a purpose, but do not expect too much from its designer's competenc </t>
+You are free to believe that the world has a purpose, but do not expect too much from its designer's competence.</t>
   </si>
   <si>
     <t xml:space="preserve">mamani2</t>
@@ -1833,7 +1837,7 @@
 弱きを助け、悪を砕くのだ！</t>
   </si>
   <si>
-    <t xml:space="preserve">Muwahahaha! ...What are you?
+    <t xml:space="preserve">Muwahahaha! ...What?
 By Opatos, I'll squash every bad bug that gets near Princess Stasha! Muwahaha!
 Long live Princess Stasha!
 I wish I was in the war 15 years ago!
@@ -3235,9 +3239,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>38</xdr:col>
-      <xdr:colOff>272520</xdr:colOff>
+      <xdr:colOff>271080</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>111240</xdr:rowOff>
+      <xdr:rowOff>109800</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3247,7 +3251,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="49651920" cy="111240"/>
+          <a:ext cx="49650480" cy="109800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4651,7 +4655,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="231.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="252.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
         <v>324</v>
       </c>

--- a/JP (Exclude Game)/Dialog/dialog.xlsx
+++ b/JP (Exclude Game)/Dialog/dialog.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="1" state="visible" r:id="rId3"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="528">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="531">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -1609,6 +1609,37 @@
 Yes #race, you're standing in front of an exile who has lived more than 1000 years.</t>
   </si>
   <si>
+    <t xml:space="preserve">oldkeep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">この城は不夜城と呼ばれて{いる}。
+城の尖塔では、夜な夜な狂宴が繰り広げられているそう{だ}。
+私もワイナン公の宴に招かれてみたいもの{だ}！
+ワイナン様の母上は…そう、とても奇抜なセンスを持った芸術家{だ}。
+気のせい{かな}？彫像や絵画に見られている気がする{のだ}。
+実にすばらしいアートの数々{だ}！
+最後にワイナン様と母上の姿を見たのは、もう何年前だろう{か}？
+この古城は、ティリス十景のひとつに数えられている{のだ}。
+ガレスは本当にろくでもないクズ{だ}。
+ガレスは正真正銘のクソったれ{だ}。あんな奴がいるから世の中おかしくなる{のだ}。
+どこにいっても薔薇の甘い香りが漂ってくる{のだ}！
+あの彫像、私の知り合いとそっくり{だ}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This castle is known as the Nevernight Castle.
+They say wild revelries take place in the castle's spires night after night.
+I'd love to be invited to one of Lord Wynan's banquets someday!
+The Lady Mother is... well, an artist with a very eccentric sense of style.
+Is it just me? I feel like the statues and paintings are watching me.
+What a magnificent collection of art!
+How many years has it been since anyone last saw Lord Wynan and the Lady Mother?
+This ancient castle is counted among the Ten Scenic Wonders of Tyris.
+Gareth is a truly rotten bastard.
+Gareth is a complete asshole. It's scum like him that makes the world such a messed-up place.
+The sweet scent of roses fills the air wherever you go!
+That statue looks exactly like someone I know.</t>
+  </si>
+  <si>
     <t xml:space="preserve">mimu</t>
   </si>
   <si>
@@ -2994,7 +3025,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3037,14 +3068,21 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="0"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <charset val="128"/>
     </font>
     <font>
@@ -3103,7 +3141,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3146,6 +3184,10 @@
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -3239,9 +3281,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>38</xdr:col>
-      <xdr:colOff>271080</xdr:colOff>
+      <xdr:colOff>270720</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>109800</xdr:rowOff>
+      <xdr:rowOff>109440</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3251,7 +3293,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="49650480" cy="109800"/>
+          <a:ext cx="49650120" cy="109440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4682,7 +4724,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr defaultColWidth="11.5078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.7"/>
@@ -4850,6 +4892,17 @@
       </c>
       <c r="D17" s="3" t="s">
         <v>365</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>368</v>
       </c>
     </row>
   </sheetData>
@@ -4902,525 +4955,525 @@
     </row>
     <row r="5" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="9" t="s">
-        <v>379</v>
+      <c r="A10" s="11" t="s">
+        <v>382</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="44.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="56.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="79.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="44.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="179.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="9" t="s">
-        <v>451</v>
+      <c r="A34" s="11" t="s">
+        <v>454</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="9" t="s">
-        <v>453</v>
-      </c>
-      <c r="C35" s="11" t="s">
-        <v>454</v>
+      <c r="A35" s="11" t="s">
+        <v>456</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>457</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="9" t="s">
-        <v>456</v>
-      </c>
-      <c r="C36" s="12" t="s">
-        <v>457</v>
+      <c r="A36" s="11" t="s">
+        <v>459</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>460</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="3" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="3" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="3" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="3" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="9" t="s">
-        <v>483</v>
+      <c r="A45" s="11" t="s">
+        <v>486</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="9" t="s">
-        <v>486</v>
+      <c r="A46" s="11" t="s">
+        <v>489</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="9" t="s">
-        <v>489</v>
+      <c r="A47" s="11" t="s">
+        <v>492</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="9" t="s">
-        <v>492</v>
+      <c r="A48" s="11" t="s">
+        <v>495</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="9" t="s">
-        <v>495</v>
+      <c r="A49" s="11" t="s">
+        <v>498</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="9" t="s">
-        <v>498</v>
+      <c r="A50" s="11" t="s">
+        <v>501</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
   </sheetData>
@@ -5473,90 +5526,90 @@
     </row>
     <row r="5" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="168.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="220.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="231.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="210.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="314.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="112.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="199.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="9" t="s">
-        <v>525</v>
+      <c r="A12" s="11" t="s">
+        <v>528</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
     </row>
   </sheetData>
